--- a/data/football_scp_master.xlsx
+++ b/data/football_scp_master.xlsx
@@ -1689,11 +1689,6 @@
           <t>2019 Topps Aaf</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>https://www.sportscardspro.com/console/football-cards-2019-topps-aaf</t>
-        </is>
-      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2296,11 +2291,6 @@
           <t>2020 Topps Xfl</t>
         </is>
       </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>https://www.sportscardspro.com/console/football-cards-2020-topps-xfl</t>
-        </is>
-      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -2327,7 +2317,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>https://www.sportscardspro.com/console/football-cards-2021-panini-chronicles-clearly-donruss-rated-rookies</t>
+          <t>https://www.sportscardspro.com/console/football-cards-2021-panini-clearly-donruss</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>https://www.sportscardspro.com/price-guide/download-custom?t=7f389d8e7c6dbb986abeec5f5789ac4a0a4cac15&amp;console-uids=G50207</t>
         </is>
       </c>
     </row>
@@ -2524,11 +2519,6 @@
           <t>2021 Panini Eminence</t>
         </is>
       </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>https://www.sportscardspro.com/console/football-cards-2021-panini-eminence</t>
-        </is>
-      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -2927,11 +2917,6 @@
           <t>2021 Pro Set Metal</t>
         </is>
       </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>https://www.sportscardspro.com/console/football-cards-2021-pro-set-metal</t>
-        </is>
-      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -2939,11 +2924,6 @@
           <t>2021 Pro Set Power</t>
         </is>
       </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>https://www.sportscardspro.com/console/football-cards-2021-pro-set-power</t>
-        </is>
-      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -2987,7 +2967,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>https://www.sportscardspro.com/console/football-cards-2022-panini-chronicles-clearly-donruss-rated-rookies</t>
+          <t>https://www.sportscardspro.com/console/football-cards-2022-panini-clearly-donruss</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>https://www.sportscardspro.com/price-guide/download-custom?t=7f389d8e7c6dbb986abeec5f5789ac4a0a4cac15&amp;console-uids=G61222</t>
         </is>
       </c>
     </row>
@@ -3830,11 +3815,6 @@
           <t>2023 Panini Immaculate Collection</t>
         </is>
       </c>
-      <c r="B203" t="inlineStr">
-        <is>
-          <t>https://www.sportscardspro.com/console/football-cards-2023-panini-immaculate-collection</t>
-        </is>
-      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -4182,11 +4162,6 @@
           <t>2023 Upper Deck Usfl</t>
         </is>
       </c>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>https://www.sportscardspro.com/console/football-cards-2023-upper-deck-usfl</t>
-        </is>
-      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -4194,11 +4169,6 @@
           <t>2023 Upper Deck Usfl Season Preview</t>
         </is>
       </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>https://www.sportscardspro.com/console/football-cards-2023-upper-deck-usfl-season-preview</t>
-        </is>
-      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -4461,11 +4431,6 @@
           <t>2024 Panini Immaculate Collection</t>
         </is>
       </c>
-      <c r="B241" t="inlineStr">
-        <is>
-          <t>https://www.sportscardspro.com/console/football-cards-2024-panini-immaculate-collection</t>
-        </is>
-      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -4815,7 +4780,12 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>https://www.sportscardspro.com/console/football-cards-2024-topps-chrome-cosmic</t>
+          <t>https://www.sportscardspro.com/console/football-cards-2024-topps-cosmic-chrome</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>https://www.sportscardspro.com/price-guide/download-custom?t=7f389d8e7c6dbb986abeec5f5789ac4a0a4cac15&amp;console-uids=G80340</t>
         </is>
       </c>
     </row>
@@ -4825,11 +4795,6 @@
           <t>2024 Topps Chrome Sapphire Edition</t>
         </is>
       </c>
-      <c r="B263" t="inlineStr">
-        <is>
-          <t>https://www.sportscardspro.com/console/football-cards-2024-topps-chrome-sapphire-edition</t>
-        </is>
-      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -4990,11 +4955,6 @@
           <t>2025 Leaf Eclectic Signature Series Mythical Prismatic Dragon Printing Plates Black</t>
         </is>
       </c>
-      <c r="B273" t="inlineStr">
-        <is>
-          <t>https://www.sportscardspro.com/console/football-cards-2025-leaf-eclectic-signature-series-mythical-prismatic-dragon-printing-plates-black</t>
-        </is>
-      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -5002,11 +4962,6 @@
           <t>2025 Leaf Eclectic Signature Series Mythical Prismatic Dragon Printing Plates Cyan</t>
         </is>
       </c>
-      <c r="B274" t="inlineStr">
-        <is>
-          <t>https://www.sportscardspro.com/console/football-cards-2025-leaf-eclectic-signature-series-mythical-prismatic-dragon-printing-plates-cyan</t>
-        </is>
-      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -5014,11 +4969,6 @@
           <t>2025 Leaf Eclectic Signature Series Mythical Prismatic Dragon Printing Plates Magenta</t>
         </is>
       </c>
-      <c r="B275" t="inlineStr">
-        <is>
-          <t>https://www.sportscardspro.com/console/football-cards-2025-leaf-eclectic-signature-series-mythical-prismatic-dragon-printing-plates-magenta</t>
-        </is>
-      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -5026,11 +4976,6 @@
           <t>2025 Leaf Eclectic Signature Series Mythical Prismatic Dragon Printing Plates Yellow</t>
         </is>
       </c>
-      <c r="B276" t="inlineStr">
-        <is>
-          <t>https://www.sportscardspro.com/console/football-cards-2025-leaf-eclectic-signature-series-mythical-prismatic-dragon-printing-plates-yellow</t>
-        </is>
-      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -5140,11 +5085,6 @@
           <t>2025 Panini Immaculate Collection</t>
         </is>
       </c>
-      <c r="B283" t="inlineStr">
-        <is>
-          <t>https://www.sportscardspro.com/console/football-cards-2025-panini-immaculate-collection</t>
-        </is>
-      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -5407,11 +5347,6 @@
           <t>2025 Score Supplemental</t>
         </is>
       </c>
-      <c r="B299" t="inlineStr">
-        <is>
-          <t>https://www.sportscardspro.com/console/football-cards-2025-panini-score-supplemental</t>
-        </is>
-      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -5436,11 +5371,6 @@
           <t>2025 Topps Chrome Cosmic</t>
         </is>
       </c>
-      <c r="B301" t="inlineStr">
-        <is>
-          <t>https://www.sportscardspro.com/console/football-cards-2025-topps-chrome-cosmic</t>
-        </is>
-      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -5450,7 +5380,12 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>https://www.sportscardspro.com/console/football-cards-2025-topps-chrome-sapphire-edition</t>
+          <t>https://www.sportscardspro.com/console/football-cards-2025-topps-chrome-sapphire</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>https://www.sportscardspro.com/price-guide/download-custom?t=7f389d8e7c6dbb986abeec5f5789ac4a0a4cac15&amp;console-uids=G95672</t>
         </is>
       </c>
     </row>
